--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
@@ -1736,7 +1736,7 @@
         <v>86</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>122</v>
@@ -2255,7 +2255,7 @@
         <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>122</v>
@@ -2774,7 +2774,7 @@
         <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>122</v>
@@ -2982,7 +2982,7 @@
         <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>122</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
@@ -1736,7 +1736,7 @@
         <v>86</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>122</v>
@@ -2255,7 +2255,7 @@
         <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>122</v>
@@ -2774,7 +2774,7 @@
         <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>122</v>
@@ -2982,7 +2982,7 @@
         <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>122</v>
